--- a/Data/g13.5a.xlsx
+++ b/Data/g13.5a.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,11 +468,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -508,7 +508,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -518,11 +518,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -543,22 +543,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4º</t>
+          <t>3º</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -568,11 +568,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -593,11 +593,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -618,11 +618,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -639,11 +639,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
